--- a/artfynd/A 26758-2022 artfynd.xlsx
+++ b/artfynd/A 26758-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26758-2022 artfynd.xlsx
+++ b/artfynd/A 26758-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66385596</v>
+        <v>81000727</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallön, 2,8 km O-ut, Upl</t>
+          <t>sydväst Rullstensberget, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624134.1409088814</v>
+        <v>623646</v>
       </c>
       <c r="R2" t="n">
-        <v>6655243.921008493</v>
+        <v>6655259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,75 +756,71 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81000734</v>
+        <v>81000728</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>sydväst Rullstensberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623390.4026524433</v>
+        <v>623594</v>
       </c>
       <c r="R3" t="n">
-        <v>6655167.909701792</v>
+        <v>6655232</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,21 +850,11 @@
           <t>2019-11-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-11-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>låga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81000727</v>
+        <v>81000729</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623646.4680762511</v>
+        <v>623388</v>
       </c>
       <c r="R4" t="n">
-        <v>6655259.050267371</v>
+        <v>6655124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +949,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -991,21 +957,11 @@
           <t>2019-11-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-11-25</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1017,12 +973,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>äldre sumpskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>låga</t>
+          <t>två murkna lågor med 5 kapslar</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1040,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81000728</v>
+        <v>125576679</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,34 +1007,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>sydväst Rullstensberget, Upl</t>
+          <t>Rullstensberget, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623593.7553526904</v>
+        <v>623627</v>
       </c>
       <c r="R5" t="n">
-        <v>6655231.764164779</v>
+        <v>6655480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,22 +1070,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,41 +1096,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81000735</v>
+        <v>66385595</v>
       </c>
       <c r="B6" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,34 +1123,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>sydväst Rullstensberget, Upl</t>
+          <t>Kallön, 2,7 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623390.4026524433</v>
+        <v>624046</v>
       </c>
       <c r="R6" t="n">
-        <v>6655167.909701792</v>
+        <v>6655341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,27 +1172,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,29 +1193,782 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>66385596</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kallön, 2,8 km O-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>624134</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6655244</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81000735</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>sydväst Rullstensberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>623390</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6655168</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Olof Hedgren</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Olof Hedgren</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>81000732</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>sydväst Rullstensberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>623440</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6655127</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>81000733</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>sydväst Rullstensberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623440</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6655127</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81000734</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>sydväst Rullstensberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623390</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6655168</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>66385548</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallön, 2,9 km O-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>624183</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6655118</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-06-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-06-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>81000736</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>sydväst Rullstensberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623371</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6655196</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-11-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
